--- a/data/data_monitoreo_curva_de_sun.xlsx
+++ b/data/data_monitoreo_curva_de_sun.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3">
@@ -457,177 +457,177 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
+          <t>GARCIA GUTIERREZ LUIS ARTURO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SANCHEZ ULLOA CESAR AUGUSTO</t>
+          <t>RAMOS RAMOS HANDY JAIR</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RAMOS RAMOS HANDY JAIR</t>
+          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GARCIA GUTIERREZ LUIS ARTURO</t>
+          <t>SANCHEZ ULLOA CESAR AUGUSTO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FIORELA KEILY GUTIERREZ CRUZ</t>
+          <t>CARBAJAL RAMOS JESUS MARINA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CARBAJAL RAMOS JESUS MARINA</t>
+          <t>FIORELA KEILY GUTIERREZ CRUZ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GONZALES VALLE SEBASTIAN</t>
+          <t>VERDE LIZARRAGA DEYSI EUFEMIA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DELGADO DELGADO RONI</t>
+          <t>OLIVA ALVA GOSSELYN NASSIRA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VERDE LIZARRAGA DEYSI EUFEMIA</t>
+          <t>JOSSY IVANA SUÁREZ ZAVALETA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OLIVA ALVA GOSSELYN NASSIRA</t>
+          <t>BAZAN TEJADA JOSE VICENTE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JOSSY IVANA SUÁREZ ZAVALETA</t>
+          <t>GONZALES VALLE SEBASTIAN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BAZAN TEJADA JOSE VICENTE</t>
+          <t>DANY DARWIN VILLACORTA SAAVEDRA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DANY DARWIN VILLACORTA SAAVEDRA</t>
+          <t>CARDENAS CAMPOJO MARY PAULA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
+          <t>ARANEDA LOPEZ MARCO VIERI</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ARANEDA LOPEZ MARCO VIERI</t>
+          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
+          <t>DELGADO DELGADO RONI</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CARDENAS CAMPOJO MARY PAULA</t>
+          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
@@ -647,16 +647,26 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>74212151</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>ROCHA SIPIRAN JHORDAN ENRIQUE</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B24" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/data_monitoreo_curva_de_sun.xlsx
+++ b/data/data_monitoreo_curva_de_sun.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4">
@@ -467,27 +467,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RAMOS RAMOS HANDY JAIR</t>
+          <t>VERDE LIZARRAGA DEYSI EUFEMIA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
+          <t>RAMOS RAMOS HANDY JAIR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -517,17 +517,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VERDE LIZARRAGA DEYSI EUFEMIA</t>
+          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12">
@@ -547,83 +547,83 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BAZAN TEJADA JOSE VICENTE</t>
+          <t>DANY DARWIN VILLACORTA SAAVEDRA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GONZALES VALLE SEBASTIAN</t>
+          <t>BAZAN TEJADA JOSE VICENTE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DANY DARWIN VILLACORTA SAAVEDRA</t>
+          <t>GONZALES VALLE SEBASTIAN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CARDENAS CAMPOJO MARY PAULA</t>
+          <t>ARANEDA LOPEZ MARCO VIERI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARANEDA LOPEZ MARCO VIERI</t>
+          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
+          <t>CARDENAS CAMPOJO MARY PAULA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DELGADO DELGADO RONI</t>
+          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
+          <t>DELGADO DELGADO RONI</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22">

--- a/data/data_monitoreo_curva_de_sun.xlsx
+++ b/data/data_monitoreo_curva_de_sun.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
@@ -487,17 +487,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SANCHEZ ULLOA CESAR AUGUSTO</t>
+          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -517,17 +517,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
+          <t>SANCHEZ ULLOA CESAR AUGUSTO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
@@ -567,17 +567,17 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GONZALES VALLE SEBASTIAN</t>
+          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -587,17 +587,17 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
+          <t>GONZALES VALLE SEBASTIAN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -607,37 +607,37 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
+          <t>JAVE CHAVEZ ANGHELO MARTIN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DELGADO DELGADO RONI</t>
+          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JAVE CHAVEZ ANGHELO MARTIN</t>
+          <t>DELGADO DELGADO RONI</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">

--- a/data/data_monitoreo_curva_de_sun.xlsx
+++ b/data/data_monitoreo_curva_de_sun.xlsx
@@ -447,67 +447,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>143</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DAVILA CORDOVA MARIBEL</t>
+          <t>GARCIA GUTIERREZ LUIS ARTURO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GARCIA GUTIERREZ LUIS ARTURO</t>
+          <t>VERDE LIZARRAGA DEYSI EUFEMIA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VERDE LIZARRAGA DEYSI EUFEMIA</t>
+          <t>DAVILA CORDOVA MARIBEL</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RAMOS RAMOS HANDY JAIR</t>
+          <t>CARBAJAL RAMOS JESUS MARINA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
+          <t>RAMOS RAMOS HANDY JAIR</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CARBAJAL RAMOS JESUS MARINA</t>
+          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -557,37 +557,37 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BAZAN TEJADA JOSE VICENTE</t>
+          <t>ARANEDA LOPEZ MARCO VIERI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
+          <t>BAZAN TEJADA JOSE VICENTE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ARANEDA LOPEZ MARCO VIERI</t>
+          <t>CARDENAS CAMPOJO MARY PAULA</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -597,37 +597,37 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CARDENAS CAMPOJO MARY PAULA</t>
+          <t>CASTILLO QUEZADA DIEGO ALONSO</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JAVE CHAVEZ ANGHELO MARTIN</t>
+          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GUERRA CALDERON ESTHEFANY NICOLLE</t>
+          <t>JAVE CHAVEZ ANGHELO MARTIN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">

--- a/data/data_monitoreo_curva_de_sun.xlsx
+++ b/data/data_monitoreo_curva_de_sun.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>174</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6">
@@ -487,27 +487,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RAMOS RAMOS HANDY JAIR</t>
+          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ANGIE BELÉN RODRÍGUEZ ZAVALA</t>
+          <t>RAMOS RAMOS HANDY JAIR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -527,27 +527,27 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OLIVA ALVA GOSSELYN NASSIRA</t>
+          <t>JOSSY IVANA SUÁREZ ZAVALETA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JOSSY IVANA SUÁREZ ZAVALETA</t>
+          <t>OLIVA ALVA GOSSELYN NASSIRA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
